--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -737,16 +728,16 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>11.1</v>
+        <v>0.1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="3" t="n">
         <v>23</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>18.2</v>
@@ -761,16 +752,16 @@
         <v>18.6</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M4" s="8" t="n">
-        <v>86.8</v>
+        <v>18.6</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>17</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>3.4</v>
@@ -807,7 +798,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>28.4</v>
@@ -834,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>15.8</v>
@@ -843,7 +834,7 @@
         <v>16.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>3.4</v>
@@ -892,7 +883,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>28.6</v>
@@ -901,7 +892,7 @@
         <v>17.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>10.8</v>
@@ -928,7 +919,7 @@
         <v>18.2</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>3</v>
@@ -943,7 +934,7 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>58</v>
+        <v>56.3</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
@@ -977,7 +968,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>30.4</v>
@@ -995,7 +986,7 @@
         <v>15.6</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>14.4</v>
@@ -1003,23 +994,23 @@
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="8" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="M7" s="8" t="n">
+      <c r="L7" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="8" t="n">
-        <v>0.4</v>
+      <c r="Q7" s="3" t="n">
+        <v>30.4</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>20.6</v>
@@ -1028,7 +1019,7 @@
         <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>656.4</v>
+        <v>56.4</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>17</v>
@@ -1039,11 +1030,11 @@
       <c r="W7" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="X7" s="8" t="n">
+      <c r="X7" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>27.8</v>
+        <v>57.8</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>14</v>
@@ -1068,17 +1059,17 @@
       <c r="E8" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>235.9</v>
+      <c r="F8" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>19.4</v>
+        <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
@@ -1087,16 +1078,16 @@
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>17.4</v>
+        <v>16.4</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>4</v>
@@ -1116,17 +1107,17 @@
       <c r="U8" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="V8" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>2.4</v>
+        <v>24.2</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>19.4</v>
@@ -1146,7 +1137,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="n">
-        <v>148.8</v>
+        <v>145.8</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>887.1</v>
@@ -1155,16 +1146,16 @@
         <v>17.2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>27.1</v>
+        <v>57.1</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>36.4</v>
+        <v>56.4</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>18.6</v>
@@ -1185,16 +1176,16 @@
         <v>16</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>142.8</v>
+        <v>145.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1196</v>
+        <v>106</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>182.6</v>
+        <v>122.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>9255.1</v>
+        <v>255.1</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>99.59999999999999</v>
@@ -1203,13 +1194,13 @@
         <v>127.2</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>971.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>26.2</v>
+        <v>56.2</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>67</v>
@@ -1247,13 +1238,13 @@
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.1</v>
+        <v>11.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>16.6</v>
@@ -1274,10 +1265,10 @@
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>90.5</v>
+        <v>20.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
@@ -1292,7 +1283,7 @@
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>5.9</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>13.4</v>
@@ -1311,7 +1302,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="3" t="n">
         <v>28.4</v>
       </c>
       <c r="E11" s="3" t="n">
@@ -1327,7 +1318,7 @@
         <v>1.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1335,11 +1326,11 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="L11" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M11" s="8" t="n">
-        <v>18.2</v>
+      <c r="M11" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
@@ -1363,7 +1354,7 @@
         <v>425.4</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>2</v>
+        <v>20.2</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>45.4</v>
@@ -1375,7 +1366,7 @@
         <v>9.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>48.9</v>
+        <v>58.9</v>
       </c>
       <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1392,7 +1383,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>28.2</v>
@@ -1401,7 +1392,7 @@
         <v>18</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>43.1</v>
+        <v>23.1</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>10.2</v>
@@ -1421,20 +1412,20 @@
       <c r="L12" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>1.9</v>
+        <v>19.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>89</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>2.8</v>
+        <v>28.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>21.6</v>
@@ -1443,10 +1434,10 @@
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>257.1</v>
+        <v>57.1</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>1.6</v>
+        <v>16.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>45.4</v>
@@ -1481,7 +1472,7 @@
         <v>26</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>11.2</v>
+        <v>17.2</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>21.6</v>
@@ -1499,7 +1490,7 @@
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>17.6</v>
@@ -1514,7 +1505,7 @@
         <v>83.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>26</v>
@@ -1567,7 +1558,7 @@
         <v>19.2</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1578,7 +1569,7 @@
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="3" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
@@ -1587,14 +1578,14 @@
       <c r="L14" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>714.5</v>
+        <v>74.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>5.8</v>
@@ -1605,7 +1596,7 @@
       <c r="R14" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="T14" s="3" t="n">
@@ -1650,7 +1641,7 @@
         <v>17.8</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11</v>
@@ -1667,7 +1658,7 @@
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="8" t="n">
+      <c r="L15" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="M15" s="3" t="n">
@@ -1741,7 +1732,7 @@
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>288.2</v>
+        <v>84.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.6</v>
@@ -1753,19 +1744,19 @@
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>909.4</v>
+        <v>904.4</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>40</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>118.2</v>
+        <v>17.2</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>138.2</v>
@@ -1774,7 +1765,7 @@
         <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>98.8</v>
+        <v>988.2</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>66.8</v>
@@ -1792,10 +1783,10 @@
         <v>95.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>102</v>
+        <v>302</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1820,7 +1811,7 @@
       <c r="F17" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G17" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1839,44 +1830,44 @@
       <c r="M17" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>19.1</v>
+      <c r="N17" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>2.7</v>
+        <v>27.6</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>11.4</v>
+        <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>51.2</v>
+        <v>53.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>1.7</v>
+        <v>17.2</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>15.5</v>
+        <v>19.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1068.5</v>
+        <v>120.1</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>810.8</v>
+        <v>902.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1892,7 +1883,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>30.4</v>
@@ -1955,13 +1946,13 @@
         <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>86</v>
+        <v>16.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1984,7 +1975,7 @@
         <v>17.8</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>23.1</v>
+        <v>23.8</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>11.8</v>
@@ -2007,17 +1998,17 @@
       <c r="M19" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="N19" s="8" t="n">
-        <v>18.1</v>
+      <c r="N19" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="8" t="n">
-        <v>92.59999999999999</v>
+      <c r="Q19" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>20.8</v>
@@ -2032,7 +2023,7 @@
         <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>19.8</v>
@@ -2041,7 +2032,7 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>294</v>
+        <v>28.2</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16</v>
@@ -2060,10 +2051,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>10.6</v>
+        <v>30.6</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>18.2</v>
@@ -2071,11 +2062,11 @@
       <c r="F20" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>87.40000000000001</v>
+      <c r="H20" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>7.9</v>
@@ -2084,7 +2075,7 @@
         <v>12.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18.8</v>
@@ -2096,7 +2087,7 @@
         <v>19</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>2.8</v>
@@ -2129,7 +2120,7 @@
         <v>58</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2152,7 +2143,7 @@
         <v>18</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2.2</v>
+        <v>22.3</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>8.6</v>
@@ -2167,7 +2158,7 @@
         <v>2.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
@@ -2176,10 +2167,10 @@
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>2.8</v>
@@ -2194,10 +2185,10 @@
         <v>19.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>56.8</v>
+        <v>56</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.4</v>
@@ -2209,7 +2200,7 @@
         <v>18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2228,7 +2219,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>28.4</v>
@@ -2255,13 +2246,13 @@
         <v>6.8</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>87</v>
@@ -2273,7 +2264,7 @@
         <v>23.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>19.5</v>
@@ -2294,10 +2285,10 @@
         <v>445.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>254.9</v>
+        <v>1.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2313,19 +2304,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>14.5</v>
+        <v>145.6</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>36.2</v>
+        <v>56.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
@@ -2340,10 +2331,10 @@
         <v>6.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>92</v>
@@ -2367,13 +2358,13 @@
         <v>468</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1123.5</v>
+        <v>123.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>935.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>26</v>
@@ -2382,7 +2373,7 @@
         <v>7050.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>652.8</v>
+        <v>62.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2411,7 +2402,7 @@
         <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2430,13 +2421,13 @@
         <v>0.1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>5.4</v>
+        <v>25.4</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q24" s="8" t="n">
-        <v>84.09999999999999</v>
+      <c r="Q24" s="3" t="n">
+        <v>28.1</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>20.7</v>
@@ -2445,25 +2436,25 @@
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.1</v>
+        <v>13.6</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>11.1</v>
+        <v>18.3</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>10.1</v>
+        <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>118.9</v>
+        <v>18.4</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>1.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2479,20 +2470,20 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1.2</v>
+        <v>19.6</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2504,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>7.6</v>
+        <v>17.6</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>16.3</v>
@@ -2541,7 +2532,7 @@
         <v>9.5</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>88.8</v>
+        <v>88</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>2.8</v>
@@ -2567,19 +2558,19 @@
         <v>17.2</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>23.9</v>
+        <v>23</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H26" s="8" t="n">
-        <v>16.8</v>
+      <c r="H26" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>8</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
@@ -2591,13 +2582,13 @@
         <v>16.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
@@ -2624,10 +2615,10 @@
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>28.8</v>
+        <v>58.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>112.8</v>
+        <v>12.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2642,21 +2633,23 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="8" t="n">
+      <c r="C27" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>27.4</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>15.2</v>
+        <v>17.2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11</v>
+        <v>16.2</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
@@ -2665,7 +2658,7 @@
         <v>6.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
@@ -2674,16 +2667,16 @@
         <v>16.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>11.8</v>
+        <v>18.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>21.4</v>
+        <v>27.4</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>20.8</v>
@@ -2692,13 +2685,13 @@
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>64.8</v>
+        <v>24.8</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>19.8</v>
@@ -2726,33 +2719,33 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>27.4</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="8" t="n">
-        <v>66</v>
+      <c r="H28" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>8.9</v>
+        <v>7.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="L28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M28" s="3" t="n">
@@ -2777,25 +2770,25 @@
         <v>20.7</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>56.9</v>
+        <v>56.7</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>29.6</v>
+        <v>25.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>17.8</v>
+        <v>19.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>59.9</v>
+        <v>59.2</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2817,7 +2810,7 @@
         <v>26.8</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>15.9</v>
+        <v>17.4</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>22.1</v>
@@ -2825,17 +2818,17 @@
       <c r="G29" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>18.6</v>
@@ -2862,7 +2855,7 @@
         <v>19.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>59.8</v>
+        <v>59.5</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>13.2</v>
@@ -2873,8 +2866,8 @@
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>19</v>
+      <c r="X29" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2909,13 +2902,13 @@
         <v>474.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>280</v>
+        <v>22</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>39.8</v>
+        <v>33</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>308.4</v>
@@ -2948,19 +2941,19 @@
         <v>298.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>10.8</v>
+        <v>70.8</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>71.59999999999999</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>916.2</v>
+        <v>336.2</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>47.6</v>
@@ -2979,7 +2972,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>26.6</v>
@@ -2994,7 +2987,7 @@
         <v>9.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1.6</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>4</v>
@@ -3004,16 +2997,16 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>205.1</v>
+        <v>25.6</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>3</v>
@@ -3022,16 +3015,16 @@
         <v>26.4</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>10.4</v>
+        <v>20.4</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>59.8</v>
+        <v>59.2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.4</v>
+        <v>14.2</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>23.6</v>
@@ -3043,10 +3036,10 @@
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3081,10 +3074,10 @@
         <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>18.4</v>
@@ -3094,7 +3087,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>4.8</v>
+        <v>29</v>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="3" t="n">
@@ -3104,10 +3097,10 @@
         <v>7.4</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>1.9</v>
+        <v>19.3</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>96.8</v>
+        <v>56.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>198.1</v>
@@ -3117,10 +3110,10 @@
         <v>449.1</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>4412.8</v>
+        <v>9119.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>81.8</v>
+        <v>26.2</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>14.6</v>
@@ -3158,7 +3151,7 @@
         <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -3166,8 +3159,8 @@
       <c r="L33" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="M33" s="8" t="n">
-        <v>19.6</v>
+      <c r="M33" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>16.7</v>
@@ -3185,13 +3178,13 @@
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>256</v>
+        <v>56</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>1.2</v>
+        <v>15.3</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21.8</v>
@@ -3206,7 +3199,7 @@
         <v>75</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3223,10 +3216,10 @@
       </c>
       <c r="C34" s="3" t="inlineStr"/>
       <c r="D34" s="3" t="n">
-        <v>48.2</v>
+        <v>28.2</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>23.1</v>
@@ -3244,9 +3237,9 @@
         <v>7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L34" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3274,7 +3267,7 @@
         <v>57.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>24.6</v>
@@ -3289,7 +3282,7 @@
         <v>67</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3304,15 +3297,17 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D35" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>28.9</v>
+        <v>17.6</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>6.6</v>
@@ -3321,7 +3316,7 @@
         <v>16.8</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>5.2</v>
@@ -3329,8 +3324,8 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="8" t="n">
-        <v>17.9</v>
+      <c r="L35" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.8</v>
@@ -3339,7 +3334,7 @@
         <v>16.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>3.4</v>
@@ -3354,7 +3349,7 @@
         <v>18.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>82.2</v>
+        <v>62.2</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.4</v>
@@ -3362,7 +3357,7 @@
       <c r="V35" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="8" t="n">
+      <c r="W35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3372,7 +3367,7 @@
         <v>86.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>11.8</v>
+        <v>18.6</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>17.2</v>
@@ -3430,7 +3425,7 @@
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3440,7 +3435,7 @@
         <v>56.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.3</v>
+        <v>17</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.4</v>
@@ -3452,7 +3447,7 @@
         <v>20.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3468,12 +3463,14 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="D37" s="3" t="n">
-        <v>120.8</v>
+        <v>132.8</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>8821.799999999999</v>
+        <v>882.1</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>11</v>
@@ -3491,7 +3488,7 @@
         <v>31.5</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>117.2</v>
+        <v>17.2</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>90.40000000000001</v>
@@ -3503,19 +3500,19 @@
         <v>0.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>20.8</v>
+        <v>30.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>149.4</v>
+        <v>14.4</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>131.8</v>
+        <v>133.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>1082.2</v>
+        <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1181.5</v>
+        <v>218.8</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>288.6</v>
@@ -3527,13 +3524,13 @@
         <v>109.8</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>998.1</v>
+        <v>95</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>101.4</v>
+        <v>1014.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3571,23 +3568,23 @@
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.8</v>
+        <v>17.9</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.9</v>
+        <v>29.9</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>26.8</v>
@@ -3599,7 +3596,7 @@
         <v>28.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>5.4</v>
+        <v>0.1</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
@@ -3608,16 +3605,16 @@
         <v>22</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>12790.1</v>
-      </c>
-      <c r="X38" s="8" t="n">
-        <v>111.9</v>
+        <v>11.1</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>1.4</v>
+        <v>11.1</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3633,7 +3630,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>463</v>
@@ -3655,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19.4</v>
@@ -3667,7 +3664,7 @@
         <v>19</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>84.8</v>
+        <v>84</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>9.6</v>
@@ -3679,10 +3676,10 @@
         <v>204.8</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>16.5</v>
@@ -3693,11 +3690,11 @@
       <c r="W39" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="X39" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>64.8</v>
+        <v>64.5</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>48.8</v>
@@ -3720,13 +3717,13 @@
         <v>26.2</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.8</v>
+        <v>7.8</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>16.4</v>
@@ -3735,10 +3732,10 @@
         <v>2.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.4</v>
+        <v>5.4</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>19.2</v>
@@ -3756,10 +3753,10 @@
         <v>3.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>16.2</v>
+        <v>26.2</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
@@ -3767,8 +3764,8 @@
       <c r="T40" s="3" t="n">
         <v>57.8</v>
       </c>
-      <c r="U40" s="8" t="n">
-        <v>94.40000000000001</v>
+      <c r="U40" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20.8</v>
@@ -3797,16 +3794,16 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>11.1</v>
+        <v>0.1</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>84.90000000000001</v>
+        <v>25.4</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2.1</v>
+        <v>21.9</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>20.1</v>
@@ -3815,7 +3812,7 @@
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
@@ -3827,43 +3824,43 @@
         <v>19.4</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15.2</v>
+        <v>17.2</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>1.8</v>
+        <v>18.3</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.9</v>
+        <v>62.2</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>11.2</v>
+        <v>19.6</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
@@ -3880,23 +3877,23 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="8" t="n">
-        <v>48.6</v>
+      <c r="D42" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="G42" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>94</v>
+      <c r="F42" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>11.6</v>
@@ -3905,9 +3902,9 @@
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M42" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M42" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -3944,10 +3941,10 @@
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>1.4</v>
+        <v>14.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>1.4</v>
+        <v>57</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3964,19 +3961,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>50.1</v>
+        <v>30.4</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>12.1</v>
+        <v>22.8</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>174.4</v>
+        <v>15.4</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>8.6</v>
@@ -3987,35 +3984,35 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="8" t="n">
+      <c r="L43" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M43" s="8" t="n">
+      <c r="M43" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>13.9</v>
+        <v>15.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>3</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>20.4</v>
+        <v>30.4</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="S43" s="8" t="n">
-        <v>18</v>
+      <c r="S43" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>42.6</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>25.9</v>
+        <v>25</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>26.4</v>
@@ -4030,7 +4027,7 @@
         <v>14.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>21.9</v>
+        <v>57</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4046,28 +4043,28 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="F44" s="8" t="n">
-        <v>12</v>
+      <c r="F44" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>26.1</v>
+        <v>14.2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>1.6</v>
+        <v>7.6</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
@@ -4076,21 +4073,21 @@
         <v>18.8</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>154.8</v>
+        <v>298.6</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="R44" s="8" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="R44" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4100,13 +4097,13 @@
         <v>47</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>2.3</v>
+        <v>23.2</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4115,7 +4112,7 @@
         <v>14.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>21</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4130,15 +4127,17 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D45" s="3" t="n">
-        <v>1165.8</v>
+        <v>167.8</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>102.8</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>135.9</v>
+        <v>135.3</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>65</v>
@@ -4147,13 +4146,13 @@
         <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>53.5</v>
+        <v>33.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>59.4</v>
+        <v>9.4</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>109.6</v>
@@ -4162,7 +4161,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>499</v>
@@ -4174,31 +4173,31 @@
         <v>16.5</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1191.1</v>
+        <v>121</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>115.2</v>
+        <v>116.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>517.9</v>
+        <v>317.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>187.1</v>
+        <v>107.1</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>1543</v>
+        <v>143</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>111.5</v>
+        <v>115</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>392.9</v>
+        <v>393.6</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>11141.1</v>
+        <v>114</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4224,7 +4223,7 @@
         <v>22.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>19.8</v>
+        <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4236,7 +4235,7 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>72162.8</v>
+        <v>280.8</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>18.3</v>
@@ -4244,14 +4243,14 @@
       <c r="M46" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="N46" s="8" t="n">
-        <v>54.9</v>
+      <c r="N46" s="3" t="n">
+        <v>2011</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>17.8</v>
+        <v>26.2</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>27.5</v>
@@ -4259,8 +4258,8 @@
       <c r="R46" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="8" t="n">
-        <v>19.8</v>
+      <c r="S46" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>53</v>
@@ -4281,7 +4280,7 @@
         <v>3.6</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
